--- a/postman-tests/Documents/Pre_Connectathon_2026_05_Test_Results.xlsx
+++ b/postman-tests/Documents/Pre_Connectathon_2026_05_Test_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bryantaustin/Projects/ecqm/fhir-cqm/postman-tests/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F95E2D4B-87E3-A541-8DDF-D400171C35F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82416443-61E4-5C44-8F0C-0751F7C4BC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-37980" yWindow="1340" windowWidth="34600" windowHeight="18980" xr2:uid="{E8D090F9-E596-4AD1-B5E4-7354F7BD68D9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="78">
   <si>
     <t>Test Name</t>
   </si>
@@ -267,6 +267,29 @@
   </si>
   <si>
     <t>removed as not required</t>
+  </si>
+  <si>
+    <t>The functionality for this test is for the future. Commented out for now.</t>
+  </si>
+  <si>
+    <t>Adjusted with new expansion</t>
+  </si>
+  <si>
+    <t>changed name to ECQMUpdate20220505</t>
+  </si>
+  <si>
+    <t>changed expansion identifier to ECQMUpdate20220505</t>
+  </si>
+  <si>
+    <t>See note in test: As of 11/29/2024 the only server I have found that supports $package is the cqf-ruler</t>
+  </si>
+  <si>
+    <t>This works for Hl7's http://tx.fhir.org/r4/ , except for publisher;
+Changed name to default-to-lastest-version
+On https://build.fhir.org/ig/HL7/cqf-measures/changes.html?#changes-to-align-with-fhir-publishing it states:
+16.6 STU3 Release for FHIR R4 (v3.0.0)
+16.6.3.4.1 Changes to align with FHIR publishing
+Required support for activeOnly, displayLanguage, limitedExpansion, and default-to-latest-version parameters in $expand</t>
   </si>
 </sst>
 </file>
@@ -700,8 +723,9 @@
     <col min="2" max="2" width="51.1640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="45.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="62.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="8.83203125" style="2"/>
+    <col min="5" max="5" width="34.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.5" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -836,6 +860,9 @@
       <c r="D8" s="9" t="s">
         <v>63</v>
       </c>
+      <c r="E8" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
@@ -850,6 +877,9 @@
       <c r="D9" s="7" t="s">
         <v>58</v>
       </c>
+      <c r="E9" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
@@ -864,6 +894,9 @@
       <c r="D10" s="9" t="s">
         <v>24</v>
       </c>
+      <c r="E10" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
@@ -878,6 +911,9 @@
       <c r="D11" s="9" t="s">
         <v>24</v>
       </c>
+      <c r="E11" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
@@ -892,6 +928,9 @@
       <c r="D12" s="7" t="s">
         <v>28</v>
       </c>
+      <c r="E12" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
@@ -906,8 +945,11 @@
       <c r="D13" s="7" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="E13" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="208" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>32</v>
       </c>
@@ -919,6 +961,9 @@
       </c>
       <c r="D14" s="9" t="s">
         <v>34</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -934,6 +979,9 @@
       <c r="D15" s="7" t="s">
         <v>35</v>
       </c>
+      <c r="E15" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
@@ -948,8 +996,11 @@
       <c r="D16" s="7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="E16" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>42</v>
       </c>
@@ -962,8 +1013,11 @@
       <c r="D17" s="7" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="E17" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>7</v>
       </c>
@@ -976,8 +1030,12 @@
       <c r="D18" s="7" t="s">
         <v>9</v>
       </c>
+      <c r="E18" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>